--- a/sheets/대금율보/검수/산조합주 진양.xlsx
+++ b/sheets/대금율보/검수/산조합주 진양.xlsx
@@ -4156,7 +4156,7 @@
         <is>
           <t xml:space="preserve">無
 –
-潢)‹</t>
+潢)</t>
         </is>
       </c>
       <c r="G5" s="26"/>
@@ -4196,7 +4196,7 @@
         <is>
           <t xml:space="preserve">林
 南)
-–⌇‹</t>
+–⌇</t>
         </is>
       </c>
       <c r="Q5" s="26"/>
@@ -4212,7 +4212,7 @@
         <is>
           <t xml:space="preserve">南)
 太
-–‹</t>
+–</t>
         </is>
       </c>
       <c r="U5" s="26"/>
@@ -4251,11 +4251,7 @@
         </is>
       </c>
       <c r="I6" s="22"/>
-      <c r="J6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J6" s="21"/>
       <c r="K6" s="22"/>
       <c r="L6" s="21" t="inlineStr">
         <is>
@@ -4268,7 +4264,7 @@
         <is>
           <t xml:space="preserve">太
 林
-–⌇‹</t>
+–⌇</t>
         </is>
       </c>
       <c r="O6" s="22"/>
@@ -4372,7 +4368,7 @@
       <c r="C8" s="26"/>
       <c r="D8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林⌇‹</t>
+          <t xml:space="preserve">林⌇</t>
         </is>
       </c>
       <c r="E8" s="26"/>
@@ -4380,13 +4376,13 @@
         <is>
           <t xml:space="preserve">無
 –
-無∧)‹</t>
+無∧)</t>
         </is>
       </c>
       <c r="G8" s="26"/>
       <c r="H8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林‹</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="I8" s="26"/>
@@ -4394,7 +4390,7 @@
         <is>
           <t xml:space="preserve">林
 –
-南‹</t>
+南</t>
         </is>
       </c>
       <c r="K8" s="26"/>
@@ -4402,7 +4398,7 @@
         <is>
           <t xml:space="preserve">無
 –
-南∧‹</t>
+南∧</t>
         </is>
       </c>
       <c r="M8" s="26"/>
@@ -4410,7 +4406,7 @@
         <is>
           <t xml:space="preserve">林
 –
-林‹</t>
+林</t>
         </is>
       </c>
       <c r="O8" s="26"/>
@@ -4607,7 +4603,7 @@
         <is>
           <t xml:space="preserve">南)
 太
-–⌇‹</t>
+–⌇</t>
         </is>
       </c>
       <c r="Q13" s="26"/>
@@ -4615,7 +4611,7 @@
         <is>
           <t xml:space="preserve">汰▾
 㳞
-㳞‹</t>
+㳞</t>
         </is>
       </c>
       <c r="S13" s="26"/>
@@ -4644,7 +4640,7 @@
         <is>
           <t xml:space="preserve">太
 –
-太∧⌇‹</t>
+太∧⌇</t>
         </is>
       </c>
       <c r="M14" s="22"/>
@@ -4674,7 +4670,7 @@
       <c r="S14" s="22"/>
       <c r="T14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋ㅅ⌇‹</t>
+          <t xml:space="preserve">淋ㅅ⌇</t>
         </is>
       </c>
       <c r="U14" s="22"/>

--- a/sheets/대금율보/검수/산조합주 진양.xlsx
+++ b/sheets/대금율보/검수/산조합주 진양.xlsx
@@ -3921,32 +3921,32 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="18.03" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="18.03" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="18.03" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="18.03" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="18.03" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="18.03" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="18.03" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="18.03" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="18.03" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="18.03" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="114.29" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3973,7 +3973,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="341.07" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
       </c>
       <c r="U3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="341.07" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="U4" s="23"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="341.07" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
       </c>
       <c r="U5" s="26"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="341.07" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="U6" s="22"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="341.07" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="U7" s="23"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="341.07" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4435,10 +4435,10 @@
       </c>
       <c r="U8" s="26"/>
     </row>
-    <row r="9">
+    <row r="9" ht="6.0" customHeight="true">
       <c r="A9" s="0"/>
     </row>
-    <row r="10" ht="60" customHeight="1">
+    <row r="10" ht="114.29" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="20" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
       <c r="T10" s="20"/>
       <c r="U10" s="20"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="341.07" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="22"/>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="U11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="341.07" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="23"/>
@@ -4571,7 +4571,7 @@
       </c>
       <c r="U12" s="23"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="341.07" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="26"/>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="U13" s="28"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="341.07" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="22"/>
@@ -4675,7 +4675,7 @@
       </c>
       <c r="U14" s="22"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="341.07" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21"/>
       <c r="C15" s="23"/>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="U15" s="23"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="341.07" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="26"/>
@@ -4788,7 +4788,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="61"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="35"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="8" max="16383" man="1"/>
   </rowBreaks>
